--- a/docs/files/REPORT_FILTRI/CR - MARTELLATO MARCO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - MARTELLATO MARCO.xlsx
@@ -684,10 +684,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>33</v>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>33</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>57</v>
@@ -863,7 +863,7 @@
         <v>54</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>5</v>
@@ -904,16 +904,16 @@
         <v>3</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>0</v>
